--- a/artfynd/A 535-2026 artfynd.xlsx
+++ b/artfynd/A 535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122067</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136122043</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136122051</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136122066</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136122074</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136122081</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125725</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>136122041</v>
       </c>
       <c r="B9" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136122037</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136122042</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136122047</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136122068</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136122082</v>
       </c>
       <c r="B15" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136125727</v>
       </c>
       <c r="B16" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>136122063</v>
       </c>
       <c r="B74" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>136125720</v>
       </c>
       <c r="B75" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>136125735</v>
       </c>
       <c r="B76" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>136125741</v>
       </c>
       <c r="B77" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 535-2026 artfynd.xlsx
+++ b/artfynd/A 535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122067</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136122043</v>
       </c>
       <c r="B3" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136122051</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136122066</v>
       </c>
       <c r="B5" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136122074</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136122081</v>
       </c>
       <c r="B7" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125725</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>136122041</v>
       </c>
       <c r="B9" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136122037</v>
       </c>
       <c r="B11" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136122042</v>
       </c>
       <c r="B12" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136122047</v>
       </c>
       <c r="B13" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136122068</v>
       </c>
       <c r="B14" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136122082</v>
       </c>
       <c r="B15" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136125727</v>
       </c>
       <c r="B16" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>136122063</v>
       </c>
       <c r="B74" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>136125720</v>
       </c>
       <c r="B75" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>136125735</v>
       </c>
       <c r="B76" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>136125741</v>
       </c>
       <c r="B77" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 535-2026 artfynd.xlsx
+++ b/artfynd/A 535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122067</v>
       </c>
       <c r="B2" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136122043</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136122051</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136122066</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136122074</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136122081</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125725</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>136122041</v>
       </c>
       <c r="B9" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136122037</v>
       </c>
       <c r="B11" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136122042</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136122047</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136122068</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136122082</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136125727</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136122035</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>136122040</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136122044</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>136122050</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136122056</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136122060</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>136122065</v>
       </c>
       <c r="B23" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>136122070</v>
       </c>
       <c r="B24" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>136122075</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>136122076</v>
       </c>
       <c r="B26" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>136122078</v>
       </c>
       <c r="B27" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136122084</v>
       </c>
       <c r="B28" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>136122089</v>
       </c>
       <c r="B29" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>136125719</v>
       </c>
       <c r="B30" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>136125722</v>
       </c>
       <c r="B31" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>136125724</v>
       </c>
       <c r="B32" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>136125726</v>
       </c>
       <c r="B33" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136125729</v>
       </c>
       <c r="B34" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136125744</v>
       </c>
       <c r="B35" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>136125745</v>
       </c>
       <c r="B36" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>136125746</v>
       </c>
       <c r="B37" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>136125748</v>
       </c>
       <c r="B38" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136125749</v>
       </c>
       <c r="B39" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>136125750</v>
       </c>
       <c r="B40" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136122055</v>
       </c>
       <c r="B41" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>136122058</v>
       </c>
       <c r="B42" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>136125742</v>
       </c>
       <c r="B43" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>136122069</v>
       </c>
       <c r="B44" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136122048</v>
       </c>
       <c r="B46" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>136122087</v>
       </c>
       <c r="B47" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>136125730</v>
       </c>
       <c r="B48" t="n">
-        <v>80593</v>
+        <v>80595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>136122038</v>
       </c>
       <c r="B49" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>136122049</v>
       </c>
       <c r="B50" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>136122034</v>
       </c>
       <c r="B51" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136122036</v>
       </c>
       <c r="B52" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>136122045</v>
       </c>
       <c r="B53" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>136122052</v>
       </c>
       <c r="B54" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>136122053</v>
       </c>
       <c r="B55" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>136122057</v>
       </c>
       <c r="B56" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>136122062</v>
       </c>
       <c r="B57" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>136122071</v>
       </c>
       <c r="B58" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136122072</v>
       </c>
       <c r="B59" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>136122073</v>
       </c>
       <c r="B60" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>136122079</v>
       </c>
       <c r="B61" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>136122080</v>
       </c>
       <c r="B62" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>136122085</v>
       </c>
       <c r="B63" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>136122086</v>
       </c>
       <c r="B64" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>136122091</v>
       </c>
       <c r="B65" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>136125723</v>
       </c>
       <c r="B66" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>136125728</v>
       </c>
       <c r="B67" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>136125740</v>
       </c>
       <c r="B68" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>136122077</v>
       </c>
       <c r="B69" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>136122059</v>
       </c>
       <c r="B70" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>136125733</v>
       </c>
       <c r="B71" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>136125734</v>
       </c>
       <c r="B72" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>136122061</v>
       </c>
       <c r="B73" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>136122063</v>
       </c>
       <c r="B74" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>136125720</v>
       </c>
       <c r="B75" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>136125735</v>
       </c>
       <c r="B76" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>136125741</v>
       </c>
       <c r="B77" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>136125743</v>
       </c>
       <c r="B78" t="n">
-        <v>79158</v>
+        <v>79160</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>136125747</v>
       </c>
       <c r="B79" t="n">
-        <v>79158</v>
+        <v>79160</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
